--- a/output/pdf_financials_xlsx/RDU.xlsx
+++ b/output/pdf_financials_xlsx/RDU.xlsx
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>6.926783</v>
+        <v>14.266046</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>0.912273</v>

--- a/output/pdf_financials_xlsx/RDU.xlsx
+++ b/output/pdf_financials_xlsx/RDU.xlsx
@@ -2245,22 +2245,22 @@
         <v>0</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.060302</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.060467</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.060467</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.060467</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.061861</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0</v>
+        <v>0.018729</v>
       </c>
     </row>
     <row r="29">
@@ -2306,22 +2306,22 @@
         <v>-1.565694</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.530142</v>
+        <v>-2.46984</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.868743</v>
+        <v>-0.808276</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.094312</v>
+        <v>1.154779</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.62601</v>
+        <v>-2.565543</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.95078</v>
+        <v>-0.888919</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-1.345932</v>
+        <v>-1.327203</v>
       </c>
     </row>
     <row r="30">
@@ -6847,22 +6847,22 @@
         <v>0</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.060302</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.060467</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.060467</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.060467</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.061861</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>0.018729</v>
       </c>
     </row>
     <row r="101">
@@ -7552,13 +7552,13 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.028199</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.024477</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.004078</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -7567,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.01472</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -22822,7 +22822,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -29496,7 +29500,11 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -30518,7 +30526,11 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -31366,7 +31378,11 @@
           <t>Loss from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -33244,7 +33260,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -34992,7 +35012,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -41436,7 +41460,11 @@
           <t>Depreciation of right-of-use asset (Note 9)</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -46078,7 +46106,11 @@
           <t>Depreciation of right-of-use asset (Note 10)</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RDU.xlsx
+++ b/output/pdf_financials_xlsx/RDU.xlsx
@@ -1386,19 +1386,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.063</v>
+        <v>0.063</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.192</v>
+        <v>-0.192</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.358533</v>
+        <v>-0.358533</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.716754</v>
+        <v>-0.716754</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -6872,7 +6872,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0.74236</v>
+        <v>0.728129</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.032729</v>
@@ -7567,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0.01472</v>
+        <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -7756,28 +7756,28 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.303996</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.045433</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.572333</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.00527</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.051175</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.03909</v>
       </c>
       <c r="S115" s="3" t="n">
-        <v>0</v>
+        <v>1.059576</v>
       </c>
     </row>
     <row r="116">
@@ -24000,7 +24000,11 @@
           <t>Proceeds from sale of equity investments</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -29500,11 +29504,7 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>SaleOfPPE</t>
-        </is>
-      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -30526,11 +30526,7 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>SaleOfPPE</t>
-        </is>
-      </c>
+      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -33988,7 +33984,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -36588,7 +36588,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -39808,7 +39812,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E300" s="5" t="n">
         <v>-0.014231</v>
       </c>
@@ -60328,7 +60336,11 @@
           <t>Deferred income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
           <t>-</t>
@@ -63948,7 +63960,11 @@
           <t>Deferred income tax recovery (Note 14)</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
           <t>-</t>
@@ -65822,7 +65838,11 @@
           <t>Future income tax recovery (expense) (Note 13)</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E553" s="5" t="n">
         <v>-0.063</v>
       </c>
